--- a/UWTestDataSampleAutomation.xlsx
+++ b/UWTestDataSampleAutomation.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\N53815\IdeaProjects\DTPolicyCreation\TestDataPolicyCreationDT\TestResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B7A4DA-C783-4C2C-A533-247EE330FB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B719C689-B238-4ADC-8A49-A9FEB27EB3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7CA1EA28-2A8C-4700-813E-5660360C80EA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{7CA1EA28-2A8C-4700-813E-5660360C80EA}"/>
   </bookViews>
   <sheets>
     <sheet name="UW Details" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="UW Datas" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'UW Datas'!$AA$2:$AC$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="282">
   <si>
     <t>Slno.</t>
   </si>
@@ -406,50 +409,491 @@
     <t>QuoteReferenceNum</t>
   </si>
   <si>
+    <t>Success</t>
+  </si>
+  <si>
     <t>What is the total declared value of Installed Computer Equipment located at this Premises?</t>
   </si>
   <si>
     <t>What is the required single item loss limit for Installed Computer Equipment located at this Premises?</t>
   </si>
   <si>
-    <t>8QLNKA</t>
-  </si>
-  <si>
-    <t>BX30089790</t>
-  </si>
-  <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>9NZ794</t>
-  </si>
-  <si>
-    <t>BX30089791</t>
-  </si>
-  <si>
-    <t>9CCD6A</t>
-  </si>
-  <si>
-    <t>BX30089825</t>
-  </si>
-  <si>
-    <t>L2DMW8</t>
-  </si>
-  <si>
-    <t>BX30089826</t>
+    <t>DXWT2K</t>
+  </si>
+  <si>
+    <t>BX30089699</t>
+  </si>
+  <si>
+    <t>A7RSJ4</t>
+  </si>
+  <si>
+    <t>BX30089780</t>
+  </si>
+  <si>
+    <t>Does the Insured have a trading (as) name?</t>
+  </si>
+  <si>
+    <t>What is the trading (as) name of the Insured?</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Saanvi Trading Pvt Ltd</t>
+  </si>
+  <si>
+    <t>Sajeev textiles</t>
+  </si>
+  <si>
+    <t>Are there any subsidiary companies to be insured under this Policy?</t>
+  </si>
+  <si>
+    <t>What is the name of the subsidiary company to be insured under this Policy?</t>
+  </si>
+  <si>
+    <t>junior Trading</t>
+  </si>
+  <si>
+    <t>Does the Insured have a secondary business activity?</t>
+  </si>
+  <si>
+    <t>What is the Insured's second business activity?</t>
+  </si>
+  <si>
+    <t>What is the estimated percentage of turnover associated with this business activity?</t>
+  </si>
+  <si>
+    <t>New Sajeev Fabrics</t>
+  </si>
+  <si>
+    <t>New Sajeev Silks</t>
+  </si>
+  <si>
+    <t>jaya textiles</t>
+  </si>
+  <si>
+    <t>New  Style Centre</t>
+  </si>
+  <si>
+    <t>New Trends Clothing Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fashion Plaza</t>
+  </si>
+  <si>
+    <t>Meridian Textile Ventures</t>
+  </si>
+  <si>
+    <t>Silverline Fabric Works</t>
+  </si>
+  <si>
+    <t>Trendloom Exports Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>Royalthread Industries</t>
+  </si>
+  <si>
+    <t>Everloom Textiles Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>Prime Ventures</t>
+  </si>
+  <si>
+    <t>Policy end date is by default 12 months, would you like to change it?</t>
+  </si>
+  <si>
+    <t>Cover End Date</t>
+  </si>
+  <si>
+    <t>What is the reason for a non-standard policy tenure?</t>
+  </si>
+  <si>
+    <t>Short Term Policy Required</t>
+  </si>
+  <si>
+    <t>Alignment to Other Renewal Dates</t>
+  </si>
+  <si>
+    <t>County Court Judgements Declaration</t>
+  </si>
+  <si>
+    <t>How many County Court Judgements or Scottish equivalents have been awarded against any proposer, director or partner of the business in the last five years?</t>
+  </si>
+  <si>
+    <t>What is the total monetary amount associated with any County Court Judgement or Scottish equivalent awarded against any proposer, director or partner of the business in the last five years?</t>
+  </si>
+  <si>
+    <t>What is the date of the most recent County Court Judgement or Scottish equivalent awarded against any proposer, director or partner of the business in the last five years?</t>
+  </si>
+  <si>
+    <t>been the subject of a recovery action by HM Revenue and Customs in the last 5 years?</t>
+  </si>
+  <si>
+    <t>How many occurrences has any proposer, director or partner of the business been the subject of a recovery action by HM Revenue and Customs in the last five years?</t>
+  </si>
+  <si>
+    <t>had any litigation brought against them or been involved in a legal or contractual dispute (including employee disputes) in their capacity as a director or officer of the company in the last 5 years?</t>
+  </si>
+  <si>
+    <t>How many occurrences has any proposer, director or partner of the business had any litigation brought against them or been involved in a legal or contractual dispute in the last five years?</t>
+  </si>
+  <si>
+    <t>Claims History in Past 5 yrs</t>
+  </si>
+  <si>
+    <t>Claim Cause</t>
+  </si>
+  <si>
+    <t>Claim Occurrence Date</t>
+  </si>
+  <si>
+    <t>Total Monetary Amount (Paid and Outstanding) Associated with this Claim</t>
+  </si>
+  <si>
+    <t>Accidental Damage, Accidental Discharge of Gas Systems, Additional Expenditure, Aircraft And Other Aerial Devices, Breakdown, Collapse, Data Reinstatement, Earthquake (Fire And Shock Risks), Escape Of Beverages, Escape Of Oil, Escape Of Water, Explosion, Failure Of Power Supply, Falling Trees, Fire, Fire (Arson), Flood, Lightning, Malicious Damage, Other, Public Utilities - (Supply Undertaking), Replacement Of Locks, Riot, Robbery Or Attempted Robbery, Smoke, Sprinkler Leakage, Storm, Subsidence Ground Heave Landslip, Terrorism, Theft Or Attempted Theft Away From Premises, Theft Or Attempted Theft From Premises, Unknown, Virus/Malicious Erasure</t>
+  </si>
+  <si>
+    <t>Accidental Damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Accidental Discharge of Gas Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Additional Expenditure</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aircraft And Other Aerial Devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Breakdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Collapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data Reinstatement</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Earthquake (Fire And Shock Risks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escape Of Beverages</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escape Of Oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escape Of Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Explosion</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Failure Of Power Supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Falling Trees</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fire (Arson)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Flood</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Malicious Damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Public Utilities - (Supply Undertaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Replacement Of Locks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Riot</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Robbery Or Attempted Robbery</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Smoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sprinkler Leakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Storm</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Subsidence Ground Heave Landslip</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Terrorism</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Theft Or Attempted Theft Away From Premises</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Theft Or Attempted Theft From Premises</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Virus/Malicious Erasure</t>
+  </si>
+  <si>
+    <t>20/02/2022</t>
+  </si>
+  <si>
+    <t>24622 - Manchester Office [digital-trading.int.hub.allianz.co.uk]</t>
+  </si>
+  <si>
+    <t>MSAJE9</t>
+  </si>
+  <si>
+    <t>T16447 - Marsh Commercial Gillingham</t>
+  </si>
+  <si>
+    <t>T78383 - DHL and ADM business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T16543 - BROMWALLLIMITED </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reshma Jayan</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alekya Reddy Vaka</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sabrina Carlotti</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Radhika Rosechandran</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Anaina Joseph</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Akhila Menon</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JefferyUAMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Faiz Farook</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mrigank Singh</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Himanshi Kaushik</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SolankiAgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vidhu Tiwari</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rohit Nirale</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PriyaTest</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Manisha Singh</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sree Resmi Sethulekshmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Midhuna Sajeev</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Abhilash Kumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Navaneeth Krishnan</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AbinManiBroker</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Parida Rojalin</t>
+  </si>
+  <si>
+    <t>Select Day One Uplift Percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T15479 - Real Estate Account </t>
+  </si>
+  <si>
+    <t>Does the Insured require Portable Computer Equipment Cover?</t>
+  </si>
+  <si>
+    <t>What is the total declared value of Portable Computer Equipment?</t>
+  </si>
+  <si>
+    <t>What is the required single item loss limit for Portable Computer Equipment?</t>
+  </si>
+  <si>
+    <t>Portable Computer Excess - Theft, attempted theft, and malicious damage</t>
+  </si>
+  <si>
+    <t>Portable Computer Excess - All other claims</t>
+  </si>
+  <si>
+    <t>£250</t>
+  </si>
+  <si>
+    <t>£150</t>
+  </si>
+  <si>
+    <t>£350</t>
+  </si>
+  <si>
+    <t>£500</t>
+  </si>
+  <si>
+    <t>£50</t>
+  </si>
+  <si>
+    <t>£100</t>
+  </si>
+  <si>
+    <t>£200</t>
+  </si>
+  <si>
+    <t>Does the Insured require Computer Media Cover?</t>
+  </si>
+  <si>
+    <t>What is the required sum insured for Computer Media Cover?</t>
+  </si>
+  <si>
+    <t>Does the Insured require Additional Expenditure Cover?</t>
+  </si>
+  <si>
+    <t>What is the required sum insured?</t>
+  </si>
+  <si>
+    <t>What is the required Indemnity Period?</t>
+  </si>
+  <si>
+    <t>Does the Insured require E-Risks Cover?</t>
+  </si>
+  <si>
+    <t>What is the required sum insured in respect of Seek Destroy &amp; Prevent Cover?</t>
+  </si>
+  <si>
+    <t>What is the required sum insured in respect of Malicious Code or Attack Cover?</t>
+  </si>
+  <si>
+    <t>Does the Insured require Breakdown Business Interruption Cover?</t>
+  </si>
+  <si>
+    <t>Gross Profit</t>
+  </si>
+  <si>
+    <t>Gross Revenue/Income</t>
+  </si>
+  <si>
+    <t>What type of Breakdown Business Interruption Cover is required?</t>
+  </si>
+  <si>
+    <t>6 months</t>
+  </si>
+  <si>
+    <t>12 months</t>
+  </si>
+  <si>
+    <t>18 months</t>
+  </si>
+  <si>
+    <t>24 months</t>
+  </si>
+  <si>
+    <t>36 months</t>
+  </si>
+  <si>
+    <t>24 hours</t>
+  </si>
+  <si>
+    <t>48 hours</t>
+  </si>
+  <si>
+    <t>Does the Insured have a Maintenance Agreement in place for Computer and Auxiliary Equipment?</t>
+  </si>
+  <si>
+    <t>Excess Period</t>
+  </si>
+  <si>
+    <t>Does the Insured require Terrorism Cover?</t>
+  </si>
+  <si>
+    <t>F3EZFV</t>
+  </si>
+  <si>
+    <t>Renewal behaviour</t>
+  </si>
+  <si>
+    <t>Autorenewal</t>
+  </si>
+  <si>
+    <t>Don't autorenew (lapse if not manually renewed)</t>
+  </si>
+  <si>
+    <t>63RLNV</t>
+  </si>
+  <si>
+    <t>BX30130803</t>
+  </si>
+  <si>
+    <t>20/02/2023</t>
+  </si>
+  <si>
+    <t>20/02/2024</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>6FFH7C</t>
+  </si>
+  <si>
+    <t>BX30130881</t>
+  </si>
+  <si>
+    <t>5JJHZY</t>
+  </si>
+  <si>
+    <t>BX30130882</t>
+  </si>
+  <si>
+    <t>6M9BPB</t>
+  </si>
+  <si>
+    <t>BX30130883</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -534,8 +978,114 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF414141"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -565,8 +1115,61 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -604,13 +1207,224 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -666,8 +1480,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -681,9 +1573,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -692,6 +1611,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -701,6 +1625,834 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D11A-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>29</xdr:col>
+          <xdr:colOff>1036364</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>793750</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>29</xdr:col>
+          <xdr:colOff>1214164</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>195025</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1032" name="Control 8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1032"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>1364886</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7298</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>7300</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>291953</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3633DD41-74AA-E621-6359-30548F8CEBAA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="51113852" y="7298"/>
+          <a:ext cx="6459482" cy="284655"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" kern="1200"/>
+            <a:t>Material Damage  Page</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>14598</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>14598</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>262759</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F308EC3-5B12-B5AB-943A-EB5F1A81D716}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="57580632" y="14598"/>
+          <a:ext cx="9707471" cy="248161"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike" kern="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Additional</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike" kern="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> Covers Page</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" u="none" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>605805</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7298</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>248161</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{524F6A76-65DA-77E7-2DF6-215B166F71C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="605805" y="7298"/>
+          <a:ext cx="6313505" cy="240863"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Account Selection Page</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1532758</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>715287</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>255460</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{257CC3AC-927C-92B8-34B1-24B80629874A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6912011" y="0"/>
+          <a:ext cx="22896494" cy="255460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Insured Details Page</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>693390</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>7298</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>270056</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DD4ABDA-FF19-2637-3D16-A1A5868E3DAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="29786608" y="0"/>
+          <a:ext cx="4795345" cy="270056"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Cover Dates Page</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>1656839</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>21897</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>277356</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2ECAF169-48EE-4ECD-6461-6A72320C4181}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="34567356" y="0"/>
+          <a:ext cx="11065058" cy="277356"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Declarations page</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>7299</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>1379482</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>306552</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A00DF09-DAC7-1932-A1E3-DC920633722E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="45617816" y="0"/>
+          <a:ext cx="6123735" cy="306552"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Claims History Page</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>284654</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF065888-FF2C-86A5-223B-150C08839199}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="67908506" y="7299"/>
+          <a:ext cx="3138505" cy="277355"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Payment Page</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1020,24 +2772,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033EB84-351C-4F67-B62A-53DD1314E9CE}">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:BM8"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.81640625" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="2" max="2" width="30.90625" customWidth="1"/>
     <col min="3" max="3" width="16.36328125" customWidth="1"/>
     <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="17.453125" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="14.1796875" customWidth="1"/>
+    <col min="9" max="9" width="25.1796875" customWidth="1"/>
     <col min="10" max="10" width="9.36328125" customWidth="1"/>
-    <col min="11" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="17.54296875" customWidth="1"/>
+    <col min="11" max="11" width="15.36328125" customWidth="1"/>
+    <col min="12" max="12" width="12.36328125" customWidth="1"/>
+    <col min="13" max="13" width="37.26953125" customWidth="1"/>
     <col min="18" max="18" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:65" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1081,10 +2833,10 @@
         <v>22</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q1" s="8" t="s">
         <v>121</v>
@@ -1096,7 +2848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -1145,17 +2897,29 @@
       <c r="P2" s="9">
         <v>40000</v>
       </c>
-      <c r="Q2" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="R2" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="S2" s="19" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q2" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="S2" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI2" s="78" t="s">
+        <v>267</v>
+      </c>
+      <c r="BK2" s="79" t="s">
+        <v>271</v>
+      </c>
+      <c r="BL2" s="80" t="s">
+        <v>272</v>
+      </c>
+      <c r="BM2" s="81" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1204,22 +2968,22 @@
       <c r="P3" s="9">
         <v>42000</v>
       </c>
-      <c r="Q3" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="R3" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="22" t="s">
+      <c r="Q3" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="R3" s="18" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S3" s="19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:65" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>9</v>
+      <c r="B4" s="24" t="s">
+        <v>205</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>72</v>
@@ -1252,7 +3016,7 @@
         <v>2345679</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="N4" s="12">
         <v>46055</v>
@@ -1263,17 +3027,13 @@
       <c r="P4" s="9">
         <v>42001</v>
       </c>
-      <c r="Q4" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="R4" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="S4" s="25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Q4" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+    </row>
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -1311,7 +3071,7 @@
         <v>2345680</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="N5" s="12">
         <v>46056</v>
@@ -1320,13 +3080,13 @@
         <v>500003</v>
       </c>
       <c r="P5" s="9">
-        <v>42102</v>
+        <v>42002</v>
       </c>
       <c r="Q5" s="12"/>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -1364,7 +3124,7 @@
         <v>2345681</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="N6" s="12">
         <v>46057</v>
@@ -1379,7 +3139,7 @@
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -1432,7 +3192,7 @@
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -1484,118 +3244,6 @@
       <c r="Q8" s="12"/>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="12">
-        <v>45751</v>
-      </c>
-      <c r="L9" s="9">
-        <v>2345679</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="N9" s="12">
-        <v>46055</v>
-      </c>
-      <c r="O9" s="16">
-        <v>500002</v>
-      </c>
-      <c r="P9" s="9">
-        <v>42001</v>
-      </c>
-      <c r="Q9" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="R9" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="S9" s="28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="12">
-        <v>45752</v>
-      </c>
-      <c r="L10" s="9">
-        <v>2345680</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="12">
-        <v>46056</v>
-      </c>
-      <c r="O10" s="16">
-        <v>500003</v>
-      </c>
-      <c r="P10" s="9">
-        <v>42102</v>
-      </c>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -1609,11 +3257,9 @@
     <hyperlink ref="F3" r:id="rId2" xr:uid="{40FF6632-F2D7-4DD2-8569-0CA17E207E6C}"/>
     <hyperlink ref="F4" r:id="rId3" xr:uid="{0DAC4933-22FA-4C10-BEE9-9C9808F70C9C}"/>
     <hyperlink ref="F5" r:id="rId4" xr:uid="{E3B76184-53A5-4516-AD8B-EE5E7FBCC486}"/>
-    <hyperlink ref="F9" r:id="rId5" xr:uid="{D1AC2E57-4AE8-47D6-AE8C-7B329211DB7C}"/>
-    <hyperlink ref="F10" r:id="rId6" xr:uid="{FA43D5AA-191E-4D64-8540-CEF402216E31}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Internal&amp;1#_x000D_</oddHeader>
   </headerFooter>
@@ -1624,19 +3270,19 @@
           <x14:formula1>
             <xm:f>Sheet1!$A$1:$A$39</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C10</xm:sqref>
+          <xm:sqref>C2:C8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AF2619EA-4FC6-4DA1-8E87-9CC1E12FCD75}">
           <x14:formula1>
             <xm:f>Sheet1!$E$17:$E$31</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M10</xm:sqref>
+          <xm:sqref>M2:M8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EAAE433E-028D-4EA2-80C9-1CFFF9E8C20B}">
           <x14:formula1>
             <xm:f>Sheet1!$B$17:$B$22</xm:f>
           </x14:formula1>
-          <xm:sqref>A15:A25 G2:G10</xm:sqref>
+          <xm:sqref>A15:A25 A9 G2:G8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1646,7 +3292,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612F6F1C-F640-4CC9-921A-B55AB58DD277}">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:AI122"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.6328125" customWidth="1"/>
@@ -1723,6 +3369,9 @@
       <c r="C6" t="s">
         <v>87</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1731,6 +3380,9 @@
       <c r="C7" t="s">
         <v>88</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1747,6 +3399,9 @@
       <c r="C9" t="s">
         <v>90</v>
       </c>
+      <c r="K9" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1755,6 +3410,9 @@
       <c r="C10" t="s">
         <v>91</v>
       </c>
+      <c r="K10" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1797,17 +3455,23 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K15" s="28" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>62</v>
+      </c>
+      <c r="K16" s="28" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.5" x14ac:dyDescent="0.25">
@@ -1953,39 +3617,692 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>171</v>
+      </c>
+      <c r="B45" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D45" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" t="s">
+        <v>175</v>
+      </c>
+      <c r="F45" t="s">
+        <v>176</v>
+      </c>
+      <c r="G45" t="s">
+        <v>177</v>
+      </c>
+      <c r="H45" t="s">
+        <v>178</v>
+      </c>
+      <c r="I45" t="s">
+        <v>179</v>
+      </c>
+      <c r="J45" t="s">
+        <v>180</v>
+      </c>
+      <c r="K45" t="s">
+        <v>181</v>
+      </c>
+      <c r="L45" t="s">
+        <v>182</v>
+      </c>
+      <c r="M45" t="s">
+        <v>183</v>
+      </c>
+      <c r="N45" t="s">
+        <v>184</v>
+      </c>
+      <c r="O45" t="s">
+        <v>185</v>
+      </c>
+      <c r="P45" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>187</v>
+      </c>
+      <c r="R45" t="s">
+        <v>188</v>
+      </c>
+      <c r="S45" t="s">
+        <v>189</v>
+      </c>
+      <c r="T45" t="s">
+        <v>190</v>
+      </c>
+      <c r="U45" t="s">
+        <v>191</v>
+      </c>
+      <c r="V45" t="s">
+        <v>192</v>
+      </c>
+      <c r="W45" t="s">
+        <v>193</v>
+      </c>
+      <c r="X45" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>198</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>199</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>200</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>201</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>202</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C54" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>177</v>
+      </c>
+      <c r="C55" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>179</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>180</v>
+      </c>
+      <c r="B58" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>181</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="E62" s="33"/>
+      <c r="F62" s="33"/>
+    </row>
+    <row r="63" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+    </row>
+    <row r="64" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>186</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="E64" s="33"/>
+      <c r="F64" s="33"/>
+    </row>
+    <row r="65" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>187</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="E65" s="33"/>
+      <c r="F65" s="28" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>188</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="E66" s="33"/>
+      <c r="F66" s="28" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>47</v>
+      </c>
+      <c r="B84" t="s">
+        <v>48</v>
+      </c>
+      <c r="C84" t="s">
+        <v>49</v>
+      </c>
+      <c r="D84" t="s">
+        <v>210</v>
+      </c>
+      <c r="E84" t="s">
+        <v>51</v>
+      </c>
+      <c r="F84" t="s">
+        <v>211</v>
+      </c>
+      <c r="G84" t="s">
+        <v>58</v>
+      </c>
+      <c r="H84" t="s">
+        <v>212</v>
+      </c>
+      <c r="I84" t="s">
+        <v>213</v>
+      </c>
+      <c r="J84" t="s">
+        <v>214</v>
+      </c>
+      <c r="K84" t="s">
+        <v>215</v>
+      </c>
+      <c r="L84" t="s">
+        <v>216</v>
+      </c>
+      <c r="M84" t="s">
+        <v>217</v>
+      </c>
+      <c r="N84" t="s">
+        <v>68</v>
+      </c>
+      <c r="O84" t="s">
+        <v>69</v>
+      </c>
+      <c r="P84" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>219</v>
+      </c>
+      <c r="R84" t="s">
+        <v>70</v>
+      </c>
+      <c r="S84" t="s">
+        <v>220</v>
+      </c>
+      <c r="T84" t="s">
+        <v>72</v>
+      </c>
+      <c r="U84" t="s">
+        <v>221</v>
+      </c>
+      <c r="V84" t="s">
+        <v>222</v>
+      </c>
+      <c r="W84" t="s">
+        <v>73</v>
+      </c>
+      <c r="X84" t="s">
+        <v>223</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>224</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB84" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC84" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD84" t="s">
+        <v>83</v>
+      </c>
+      <c r="AE84" t="s">
+        <v>226</v>
+      </c>
+      <c r="AF84" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG84" t="s">
+        <v>228</v>
+      </c>
+      <c r="AH84" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI84" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>48</v>
+      </c>
+      <c r="B89" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>49</v>
+      </c>
+      <c r="B90" s="27">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>210</v>
+      </c>
+      <c r="B91" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>51</v>
+      </c>
+      <c r="B92" s="27">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>211</v>
+      </c>
+      <c r="B93" s="27">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>58</v>
+      </c>
+      <c r="B94" s="27">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="95" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>212</v>
+      </c>
+      <c r="B95" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>213</v>
+      </c>
+      <c r="B96" s="27">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" s="27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -2007,144 +4324,443 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D488D9F-3CAD-4651-8E20-3C68B9E3AA7D}">
-  <dimension ref="A1:T15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9841960-28F1-4D4D-8097-B293B1A1FD66}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.90625" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="17.453125" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="13" width="25.1796875" customWidth="1"/>
+    <col min="14" max="14" width="9.36328125" customWidth="1"/>
+    <col min="15" max="15" width="15.36328125" customWidth="1"/>
+    <col min="16" max="16" width="12.36328125" customWidth="1"/>
+    <col min="17" max="17" width="27.7265625" customWidth="1"/>
+    <col min="18" max="18" width="37.26953125" customWidth="1"/>
+    <col min="19" max="19" width="27.453125" customWidth="1"/>
+    <col min="20" max="20" width="30.54296875" customWidth="1"/>
+    <col min="21" max="21" width="10.26953125" customWidth="1"/>
+    <col min="22" max="22" width="13.81640625" customWidth="1"/>
+    <col min="23" max="23" width="11.54296875" customWidth="1"/>
+    <col min="24" max="24" width="19.08984375" customWidth="1"/>
+    <col min="25" max="25" width="23.81640625" customWidth="1"/>
+    <col min="26" max="33" width="19.7265625" customWidth="1"/>
+    <col min="34" max="34" width="28.54296875" customWidth="1"/>
+    <col min="35" max="39" width="19.7265625" customWidth="1"/>
+    <col min="55" max="55" width="16.26953125" customWidth="1"/>
+    <col min="61" max="61" width="36.26953125" customWidth="1"/>
+    <col min="62" max="62" width="12.1796875" customWidth="1"/>
+    <col min="63" max="63" width="14.453125" customWidth="1"/>
+    <col min="64" max="64" width="11.54296875" customWidth="1"/>
+    <col min="66" max="66" width="23.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:64" s="1" customFormat="1" ht="62.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="K1" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="L1" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="M1" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="O1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="P1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="Q1" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="R1" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="S1" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="T1" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="U1" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="V1" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="P1" s="15" t="s">
+      <c r="W1" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="X1" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y1" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z1" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA1" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB1" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="AC1" s="52" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD1" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE1" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="AF1" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="AG1" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH1" s="54" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI1" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="AJ1" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK1" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="AL1" s="56" t="s">
+        <v>231</v>
+      </c>
+      <c r="AM1" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="AN1" s="57" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO1" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="AP1" s="58" t="s">
+        <v>234</v>
+      </c>
+      <c r="AQ1" s="58" t="s">
+        <v>235</v>
+      </c>
+      <c r="AR1" s="58" t="s">
+        <v>236</v>
+      </c>
+      <c r="AS1" s="58" t="s">
+        <v>237</v>
+      </c>
+      <c r="AT1" s="59" t="s">
+        <v>245</v>
+      </c>
+      <c r="AU1" s="59" t="s">
+        <v>246</v>
+      </c>
+      <c r="AV1" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="AW1" s="59" t="s">
+        <v>248</v>
+      </c>
+      <c r="AX1" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="AY1" s="59" t="s">
+        <v>250</v>
+      </c>
+      <c r="AZ1" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA1" s="59" t="s">
+        <v>252</v>
+      </c>
+      <c r="BB1" s="59" t="s">
+        <v>253</v>
+      </c>
+      <c r="BC1" s="59" t="s">
+        <v>256</v>
+      </c>
+      <c r="BD1" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="BE1" s="59" t="s">
+        <v>248</v>
+      </c>
+      <c r="BF1" s="59" t="s">
+        <v>264</v>
+      </c>
+      <c r="BG1" s="59" t="s">
+        <v>265</v>
+      </c>
+      <c r="BH1" s="59" t="s">
+        <v>266</v>
+      </c>
+      <c r="BI1" s="86" t="s">
+        <v>268</v>
+      </c>
+      <c r="BJ1" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="BK1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="BL1" s="61" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+    <row r="2" spans="1:64" ht="16" x14ac:dyDescent="0.4">
+      <c r="A2" s="62">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="B2" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="K2" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="M2" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="N2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="12">
+      <c r="O2" s="39">
         <v>45749</v>
       </c>
-      <c r="L2" s="9">
+      <c r="P2" s="34">
         <v>345679</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="Q2" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="N2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" s="16">
+      <c r="R2" s="34">
+        <v>40</v>
+      </c>
+      <c r="S2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="U2" s="34">
+        <v>60</v>
+      </c>
+      <c r="V2" s="39">
+        <v>46146</v>
+      </c>
+      <c r="W2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="X2" s="39">
+        <v>46511</v>
+      </c>
+      <c r="Y2" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA2" s="34">
+        <v>2</v>
+      </c>
+      <c r="AB2" s="34">
+        <v>5000</v>
+      </c>
+      <c r="AC2" s="39">
+        <v>46055</v>
+      </c>
+      <c r="AD2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE2" s="40">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG2" s="41">
+        <v>2</v>
+      </c>
+      <c r="AH2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI2" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="AJ2" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="AK2" s="34">
+        <v>50000</v>
+      </c>
+      <c r="AL2" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="AM2" s="41">
         <v>500000</v>
       </c>
-      <c r="P2" s="9">
-        <v>40000</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="R2" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="S2" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="T2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="AN2" s="34">
+        <v>42001</v>
+      </c>
+      <c r="AO2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP2" s="43">
+        <v>23453</v>
+      </c>
+      <c r="AQ2" s="43">
+        <v>234</v>
+      </c>
+      <c r="AR2" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS2" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="AT2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AU2" s="34">
+        <v>234</v>
+      </c>
+      <c r="AV2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW2" s="34">
+        <v>2453</v>
+      </c>
+      <c r="AX2" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="AY2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ2" s="34">
+        <v>244</v>
+      </c>
+      <c r="BA2" s="34">
+        <v>242</v>
+      </c>
+      <c r="BB2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC2" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="BD2" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="BE2" s="34">
+        <v>3422</v>
+      </c>
+      <c r="BF2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG2" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="BH2" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI2" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="BJ2" s="87" t="s">
+        <v>276</v>
+      </c>
+      <c r="BK2" s="88" t="s">
+        <v>277</v>
+      </c>
+      <c r="BL2" s="89" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:64" ht="16" x14ac:dyDescent="0.4">
+      <c r="A3" s="63">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>9</v>
+      <c r="B3" s="29" t="s">
+        <v>232</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>26</v>
@@ -2162,48 +4778,183 @@
         <v>35</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>36</v>
+        <v>133</v>
       </c>
       <c r="J3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="N3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="12">
+      <c r="O3" s="12">
         <v>45660</v>
       </c>
-      <c r="L3" s="9">
+      <c r="P3" s="9">
         <v>3245679</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="N3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="16">
+      <c r="R3" s="9">
+        <v>20</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="T3" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="U3" s="9">
+        <v>80</v>
+      </c>
+      <c r="V3" s="39">
+        <v>46146</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="X3" s="39">
+        <v>46512</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA3" s="34">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="34">
+        <v>5001</v>
+      </c>
+      <c r="AC3" s="39">
+        <v>46056</v>
+      </c>
+      <c r="AD3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AE3" s="40">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG3" s="9">
+        <v>2</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="AJ3" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="AK3" s="16">
         <v>500001</v>
       </c>
-      <c r="P3" s="9">
+      <c r="AL3" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="AM3" s="9">
         <v>42000</v>
       </c>
-      <c r="Q3" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="R3" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="S3" s="28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="AN3" s="34">
+        <v>3456</v>
+      </c>
+      <c r="AO3" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP3" s="43">
+        <v>23454</v>
+      </c>
+      <c r="AQ3" s="43">
+        <v>235</v>
+      </c>
+      <c r="AR3" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS3" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="AT3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU3" s="9">
+        <v>345</v>
+      </c>
+      <c r="AV3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AW3" s="34">
+        <v>2454</v>
+      </c>
+      <c r="AX3" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="AY3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ3" s="34">
+        <v>245</v>
+      </c>
+      <c r="BA3" s="34">
+        <v>243</v>
+      </c>
+      <c r="BB3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="BC3" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="BD3" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="BE3" s="9">
+        <v>3456</v>
+      </c>
+      <c r="BF3" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG3" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="BH3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="BI3" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="BJ3" s="90" t="s">
+        <v>278</v>
+      </c>
+      <c r="BK3" s="91" t="s">
+        <v>279</v>
+      </c>
+      <c r="BL3" s="92" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:64" ht="16" x14ac:dyDescent="0.4">
+      <c r="A4" s="63">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>9</v>
+      <c r="B4" s="29" t="s">
+        <v>208</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>31</v>
@@ -2224,42 +4975,177 @@
         <v>16</v>
       </c>
       <c r="J4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="N4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="12">
+      <c r="O4" s="12">
         <v>45751</v>
       </c>
-      <c r="L4" s="9">
+      <c r="P4" s="9">
         <v>2345679</v>
       </c>
-      <c r="M4" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="N4" s="12">
-        <v>46055</v>
-      </c>
-      <c r="O4" s="16">
+      <c r="Q4" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="R4" s="9">
+        <v>60</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="U4" s="9">
+        <v>40</v>
+      </c>
+      <c r="V4" s="39">
+        <v>46147</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="X4" s="39">
+        <v>46513</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA4" s="34">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="34">
+        <v>5002</v>
+      </c>
+      <c r="AC4" s="39">
+        <v>46057</v>
+      </c>
+      <c r="AD4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AE4" s="40">
+        <v>2</v>
+      </c>
+      <c r="AF4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG4" s="85">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI4" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="AJ4" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="AK4" s="16">
         <v>500002</v>
       </c>
-      <c r="P4" s="9">
-        <v>42001</v>
-      </c>
-      <c r="Q4" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="R4" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="S4" s="28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="AL4" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="AM4" s="9">
+        <v>42401</v>
+      </c>
+      <c r="AN4" s="34">
+        <v>3457</v>
+      </c>
+      <c r="AO4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP4" s="43">
+        <v>23455</v>
+      </c>
+      <c r="AQ4" s="43">
+        <v>2165</v>
+      </c>
+      <c r="AR4" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="AS4" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="AT4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AU4" s="9">
+        <v>346</v>
+      </c>
+      <c r="AV4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW4" s="34">
+        <v>2455</v>
+      </c>
+      <c r="AX4" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="AY4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ4" s="34">
+        <v>246</v>
+      </c>
+      <c r="BA4" s="34">
+        <v>244</v>
+      </c>
+      <c r="BB4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC4" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BD4" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="BE4" s="9">
+        <v>3444</v>
+      </c>
+      <c r="BF4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG4" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="BH4" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI4" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="BJ4" s="93" t="s">
+        <v>280</v>
+      </c>
+      <c r="BK4" s="94" t="s">
+        <v>281</v>
+      </c>
+      <c r="BL4" s="95" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:64" ht="16" x14ac:dyDescent="0.4">
+      <c r="A5" s="63">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>9</v>
+      <c r="B5" s="29" t="s">
+        <v>207</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>69</v>
@@ -2274,7 +5160,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>103</v>
@@ -2283,36 +5169,171 @@
         <v>99</v>
       </c>
       <c r="J5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="12">
+      <c r="O5" s="12">
         <v>45752</v>
       </c>
-      <c r="L5" s="9">
+      <c r="P5" s="9">
         <v>2345680</v>
       </c>
-      <c r="M5" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="N5" s="12">
-        <v>46056</v>
-      </c>
-      <c r="O5" s="16">
+      <c r="Q5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" s="9">
+        <v>10</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="U5" s="9">
+        <v>90</v>
+      </c>
+      <c r="V5" s="39">
+        <v>46060</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="X5" s="39">
+        <v>46514</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA5" s="34">
+        <v>2</v>
+      </c>
+      <c r="AB5" s="34">
+        <v>5003</v>
+      </c>
+      <c r="AC5" s="39">
+        <v>46058</v>
+      </c>
+      <c r="AD5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE5" s="40">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG5" s="9">
+        <v>3</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="AJ5" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="AK5" s="16">
         <v>500003</v>
       </c>
-      <c r="P5" s="9">
-        <v>42102</v>
-      </c>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="9">
+      <c r="AL5" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="AM5" s="9">
+        <v>42002</v>
+      </c>
+      <c r="AN5" s="34">
+        <v>3458</v>
+      </c>
+      <c r="AO5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP5" s="43">
+        <v>23456</v>
+      </c>
+      <c r="AQ5" s="43">
+        <v>237</v>
+      </c>
+      <c r="AR5" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS5" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="AT5" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU5" s="9">
+        <v>347</v>
+      </c>
+      <c r="AV5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW5" s="34">
+        <v>2456</v>
+      </c>
+      <c r="AX5" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="AY5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ5" s="34">
+        <v>247</v>
+      </c>
+      <c r="BA5" s="34">
+        <v>245</v>
+      </c>
+      <c r="BB5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC5" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BD5" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE5" s="9">
+        <v>3454</v>
+      </c>
+      <c r="BF5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG5" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="BH5" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI5" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="BJ5" s="83"/>
+      <c r="BK5" s="9"/>
+      <c r="BL5" s="64"/>
+    </row>
+    <row r="6" spans="1:64" ht="16" x14ac:dyDescent="0.4">
+      <c r="A6" s="63">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>9</v>
+      <c r="B6" s="29" t="s">
+        <v>208</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>51</v>
@@ -2336,39 +5357,174 @@
         <v>100</v>
       </c>
       <c r="J6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="K6" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="12">
+      <c r="O6" s="12">
         <v>45753</v>
       </c>
-      <c r="L6" s="9">
+      <c r="P6" s="9">
         <v>2345681</v>
       </c>
-      <c r="M6" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="N6" s="12">
-        <v>46057</v>
-      </c>
-      <c r="O6" s="16">
+      <c r="Q6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" s="9">
+        <v>80</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="U6" s="9">
+        <v>20</v>
+      </c>
+      <c r="V6" s="39">
+        <v>46150</v>
+      </c>
+      <c r="W6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="X6" s="39">
+        <v>46668</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA6" s="34">
+        <v>2</v>
+      </c>
+      <c r="AB6" s="34">
+        <v>5004</v>
+      </c>
+      <c r="AC6" s="39">
+        <v>46059</v>
+      </c>
+      <c r="AD6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE6" s="40">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG6" s="9">
+        <v>4</v>
+      </c>
+      <c r="AH6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI6" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ6" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="AK6" s="16">
         <v>250004</v>
       </c>
-      <c r="P6" s="9">
+      <c r="AL6" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="AM6" s="9">
         <v>42013</v>
       </c>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="9">
+      <c r="AN6" s="34">
+        <v>3459</v>
+      </c>
+      <c r="AO6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP6" s="43">
+        <v>23457</v>
+      </c>
+      <c r="AQ6" s="43">
+        <v>238</v>
+      </c>
+      <c r="AR6" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="AS6" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="AT6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AU6" s="9">
+        <v>348</v>
+      </c>
+      <c r="AV6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW6" s="34">
+        <v>2457</v>
+      </c>
+      <c r="AX6" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="AY6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ6" s="34">
+        <v>248</v>
+      </c>
+      <c r="BA6" s="34">
+        <v>246</v>
+      </c>
+      <c r="BB6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC6" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="BD6" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE6" s="9">
+        <v>656</v>
+      </c>
+      <c r="BF6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG6" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="BH6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI6" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="BJ6" s="83"/>
+      <c r="BK6" s="9"/>
+      <c r="BL6" s="64"/>
+    </row>
+    <row r="7" spans="1:64" ht="16" x14ac:dyDescent="0.4">
+      <c r="A7" s="63">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>9</v>
+      <c r="B7" s="29" t="s">
+        <v>207</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>97</v>
@@ -2389,240 +5545,489 @@
         <v>101</v>
       </c>
       <c r="J7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="12">
+      <c r="O7" s="12">
         <v>45754</v>
       </c>
-      <c r="L7" s="9">
+      <c r="P7" s="9">
         <v>2345682</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="Q7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="N7" s="12">
-        <v>46058</v>
-      </c>
-      <c r="O7" s="16">
+      <c r="R7" s="9">
+        <v>50</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="U7" s="9">
+        <v>50</v>
+      </c>
+      <c r="V7" s="39">
+        <v>46151</v>
+      </c>
+      <c r="W7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="X7" s="39">
+        <v>46516</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA7" s="34">
+        <v>2</v>
+      </c>
+      <c r="AB7" s="34">
+        <v>5005</v>
+      </c>
+      <c r="AC7" s="39">
+        <v>46060</v>
+      </c>
+      <c r="AD7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE7" s="40">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG7" s="9">
+        <v>2</v>
+      </c>
+      <c r="AH7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI7" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="AJ7" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="AK7" s="16">
         <v>420005</v>
       </c>
-      <c r="P7" s="9">
+      <c r="AL7" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="AM7" s="9">
         <v>42004</v>
       </c>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="AN7" s="34">
+        <v>3460</v>
+      </c>
+      <c r="AO7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP7" s="43">
+        <v>23458</v>
+      </c>
+      <c r="AQ7" s="43">
+        <v>239</v>
+      </c>
+      <c r="AR7" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="AS7" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="AT7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AU7" s="9">
+        <v>349</v>
+      </c>
+      <c r="AV7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW7" s="34">
+        <v>2458</v>
+      </c>
+      <c r="AX7" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="AY7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ7" s="34">
+        <v>249</v>
+      </c>
+      <c r="BA7" s="34">
+        <v>247</v>
+      </c>
+      <c r="BB7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC7" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="BD7" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE7" s="9">
+        <v>4355</v>
+      </c>
+      <c r="BF7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG7" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="BH7" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI7" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="BJ7" s="83"/>
+      <c r="BK7" s="9"/>
+      <c r="BL7" s="64"/>
+    </row>
+    <row r="8" spans="1:64" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="65">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="B8" s="66" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="K8" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="L8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="M8" s="71" t="s">
+        <v>152</v>
+      </c>
+      <c r="N8" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="12">
+      <c r="O8" s="72">
         <v>45755</v>
       </c>
-      <c r="L8" s="9">
+      <c r="P8" s="67">
         <v>2345683</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="Q8" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="N8" s="12">
-        <v>46059</v>
-      </c>
-      <c r="O8" s="16">
+      <c r="R8" s="67">
+        <v>40</v>
+      </c>
+      <c r="S8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="T8" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="U8" s="67">
+        <v>60</v>
+      </c>
+      <c r="V8" s="39">
+        <v>46152</v>
+      </c>
+      <c r="W8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="X8" s="39">
+        <v>46517</v>
+      </c>
+      <c r="Y8" s="67" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA8" s="34">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="34">
+        <v>5006</v>
+      </c>
+      <c r="AC8" s="39">
+        <v>46061</v>
+      </c>
+      <c r="AD8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE8" s="40">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG8" s="67">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI8" s="67" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ8" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="AK8" s="73">
         <v>500006</v>
       </c>
-      <c r="P8" s="9">
+      <c r="AL8" s="74">
+        <v>0.2</v>
+      </c>
+      <c r="AM8" s="67">
         <v>42005</v>
       </c>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="12">
-        <v>45751</v>
-      </c>
-      <c r="L9" s="9">
-        <v>2345679</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="N9" s="12">
-        <v>46055</v>
-      </c>
-      <c r="O9" s="16">
-        <v>500002</v>
-      </c>
-      <c r="P9" s="9">
-        <v>42001</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="R9" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="S9" s="28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="12">
-        <v>45752</v>
-      </c>
-      <c r="L10" s="9">
-        <v>2345680</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="12">
-        <v>46056</v>
-      </c>
-      <c r="O10" s="16">
-        <v>500003</v>
-      </c>
-      <c r="P10" s="9">
-        <v>42102</v>
-      </c>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="T14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="T15" t="s">
-        <v>134</v>
-      </c>
+      <c r="AN8" s="34">
+        <v>3461</v>
+      </c>
+      <c r="AO8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP8" s="43">
+        <v>23459</v>
+      </c>
+      <c r="AQ8" s="43">
+        <v>240</v>
+      </c>
+      <c r="AR8" s="75" t="s">
+        <v>239</v>
+      </c>
+      <c r="AS8" s="67" t="s">
+        <v>242</v>
+      </c>
+      <c r="AT8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="AU8" s="9">
+        <v>350</v>
+      </c>
+      <c r="AV8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW8" s="34">
+        <v>2459</v>
+      </c>
+      <c r="AX8" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="AY8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="AZ8" s="34">
+        <v>250</v>
+      </c>
+      <c r="BA8" s="34">
+        <v>248</v>
+      </c>
+      <c r="BB8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC8" s="67" t="s">
+        <v>254</v>
+      </c>
+      <c r="BD8" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE8" s="67">
+        <v>3657</v>
+      </c>
+      <c r="BF8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="BG8" s="67" t="s">
+        <v>262</v>
+      </c>
+      <c r="BH8" s="67" t="s">
+        <v>131</v>
+      </c>
+      <c r="BI8" s="67" t="s">
+        <v>269</v>
+      </c>
+      <c r="BJ8" s="84"/>
+      <c r="BK8" s="67"/>
+      <c r="BL8" s="76"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2" xr:uid="{1269F401-3BA7-4B6C-9A0B-7A9C28858D5F}">
-      <formula1>$T$14:$T$15</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D26:D27 D19" xr:uid="{6C15ED14-AF9F-4077-ADAC-71E1ACDC60F2}">
+      <formula1>$C$2</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{334CED3C-721F-43E3-AA16-E6EC3963B757}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{5C763C2C-BDD7-4EC5-A008-836A5F3F39E9}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{3ECDD2B6-A7F9-41D7-95B5-B153C8D06BA5}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{5B8BB0CD-715A-4D43-8DD1-D2A0CA302950}"/>
-    <hyperlink ref="F9" r:id="rId5" xr:uid="{5158E2C4-7D9C-4E40-A753-0D00E5BAB5B1}"/>
-    <hyperlink ref="F10" r:id="rId6" xr:uid="{A92751EA-C759-4366-A364-03323AF4CA4D}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{42BE6B2B-5159-4A00-8FC4-9A57513A7C90}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{D41D2726-8BB3-412A-BB97-324A20746B67}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{36C21A87-6634-4069-A237-2D266407C699}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{ED8AF6E9-8F61-4307-BDBD-467FC99AF13C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
+  <drawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1032" r:id="rId8" name="Control 8">
+          <controlPr defaultSize="0" autoPict="0" r:id="rId9">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>29</xdr:col>
+                <xdr:colOff>1035050</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>29</xdr:col>
+                <xdr:colOff>1244600</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>25400</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1032" r:id="rId8" name="Control 8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB7461C4-24F9-49B0-9428-0F82D8EEF01A}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="15">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FA0AAD60-B4E8-4D46-88B9-BC350D57688D}">
           <x14:formula1>
             <xm:f>Sheet1!$B$17:$B$22</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G10</xm:sqref>
+          <xm:sqref>A15:A25 A9 G2:G8</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9FC26EA-AFF8-4007-864B-1EB4BE5E4AB9}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BF6D0764-65F7-4E21-92F5-B5825D910540}">
           <x14:formula1>
             <xm:f>Sheet1!$E$17:$E$31</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M10</xm:sqref>
+          <xm:sqref>Q2:Q8 T2:T8</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7D795A13-82C5-462F-9929-21BE5B8A72BB}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CC71668F-3FC9-4130-8B7E-878585CB43FC}">
           <x14:formula1>
             <xm:f>Sheet1!$A$1:$A$39</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C10</xm:sqref>
+          <xm:sqref>C3:C8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FAB0B86E-1A13-4217-B528-0EEF6463C977}">
+          <x14:formula1>
+            <xm:f>Sheet1!$K$9:$K$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J8 L2:L8 S2:S8 W2:W8 Z2:Z8 AD2:AD8 AF2:AF8 AH2:AH8 AO2:AO8 AT2:AT8 AV2:AV8 AY2:AY8 BB2:BB8 BF2:BF8 BH2:BH8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{998E0D3D-D65C-4771-B521-888C7F759055}">
+          <x14:formula1>
+            <xm:f>Sheet1!$F$6:$F$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>Y2:Y8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DCB170E7-0E58-4BAC-A1A5-ED9CB1978AA6}">
+          <x14:formula1>
+            <xm:f>Sheet1!$A$49:$A$81</xm:f>
+          </x14:formula1>
+          <xm:sqref>AI2:AI8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1B69B2AC-8F53-46E4-820E-CA10ACA0DBB6}">
+          <x14:formula1>
+            <xm:f>Sheet1!$A$88:$A$122</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{099E7C67-C977-4BA5-98FA-0BC83BF65C52}">
+          <x14:formula1>
+            <xm:f>Sheet1!$B$89:$B$97</xm:f>
+          </x14:formula1>
+          <xm:sqref>AL2:AL8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9EC96C1A-FDF1-45D1-BC93-83A57A824A24}">
+          <x14:formula1>
+            <xm:f>Sheet1!$C$53:$C$56</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8E43C12E-2CDE-4560-A7DD-BB25A5D7E607}">
+          <x14:formula1>
+            <xm:f>Sheet1!$C$58:$C$61</xm:f>
+          </x14:formula1>
+          <xm:sqref>AR2:AR8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{195A63B2-8018-4B8F-BC32-8685CD25E1FA}">
+          <x14:formula1>
+            <xm:f>Sheet1!$C$62:$C$64</xm:f>
+          </x14:formula1>
+          <xm:sqref>AS2:AS8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B4FA55D4-2555-46C9-B6FE-2D49ABB0293B}">
+          <x14:formula1>
+            <xm:f>Sheet1!$B$57:$B$58</xm:f>
+          </x14:formula1>
+          <xm:sqref>BC2:BC8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{448C754B-1C25-4CC5-BB34-360D32BF0660}">
+          <x14:formula1>
+            <xm:f>Sheet1!$D$62:$D$66</xm:f>
+          </x14:formula1>
+          <xm:sqref>BD2:BD8 AX2:AX8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{595DD0A4-9ACE-4347-8E73-B1248A50D96A}">
+          <x14:formula1>
+            <xm:f>Sheet1!$F$65:$F$66</xm:f>
+          </x14:formula1>
+          <xm:sqref>BG2:BG8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E54BB491-3254-433F-81AB-25780736A80B}">
+          <x14:formula1>
+            <xm:f>Sheet1!$K$15:$K$16</xm:f>
+          </x14:formula1>
+          <xm:sqref>BI2:BI8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
